--- a/Result/profitability/9949.xlsx
+++ b/Result/profitability/9949.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.47</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6050000000000001</v>
+        <v>0.615</v>
       </c>
       <c r="N2" t="n">
-        <v>59.535</v>
+        <v>59.34125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.15</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6537500000000001</v>
+        <v>0.7225</v>
       </c>
       <c r="N3" t="n">
-        <v>60.72</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.35</v>
       </c>
       <c r="M4" t="n">
-        <v>0.69875</v>
+        <v>0.70875</v>
       </c>
       <c r="N4" t="n">
-        <v>67.18125000000001</v>
+        <v>67.80375000000001</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.22</v>
       </c>
       <c r="M5" t="n">
-        <v>0.75625</v>
+        <v>0.8375000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>68.8275</v>
+        <v>69.36624999999999</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>0.25</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8887499999999999</v>
+        <v>0.05</v>
       </c>
       <c r="N6" t="n">
-        <v>70.325</v>
+        <v>68.7075</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.14</v>
       </c>
       <c r="M7" t="n">
-        <v>0.08750000000000011</v>
+        <v>0.09375</v>
       </c>
       <c r="N7" t="n">
-        <v>69.93375</v>
+        <v>69.67375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.06</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1212500000000001</v>
+        <v>0.0975</v>
       </c>
       <c r="N8" t="n">
-        <v>70.7975</v>
+        <v>70.3925</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0.53</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1837500000000001</v>
+        <v>0.18375</v>
       </c>
       <c r="N9" t="n">
         <v>71.71875</v>
@@ -1645,7 +1645,7 @@
         <v>0.43</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1787500000000001</v>
+        <v>0.17875</v>
       </c>
       <c r="N10" t="n">
         <v>71.9525</v>
@@ -1772,7 +1772,7 @@
         <v>0.17</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1812500000000001</v>
+        <v>0.18125</v>
       </c>
       <c r="N11" t="n">
         <v>71.99125000000001</v>
@@ -1899,7 +1899,7 @@
         <v>0.02</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2275000000000001</v>
+        <v>0.2275</v>
       </c>
       <c r="N12" t="n">
         <v>72.01375</v>
@@ -2026,7 +2026,7 @@
         <v>0.33</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2412500000000001</v>
+        <v>0.24125</v>
       </c>
       <c r="N13" t="n">
         <v>72.1075</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>9949</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>36</v>
+      </c>
+      <c r="D75" t="n">
+        <v>14</v>
+      </c>
+      <c r="E75" t="n">
+        <v>23</v>
+      </c>
+      <c r="F75" t="n">
+        <v>62.76</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-9</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-24.48%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-7</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.5262500000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>58.505</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-6.333333333333334</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-3.240000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.04909090909090907</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.8024691358024691</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.309999999999995</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.07373823781009392</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
